--- a/files/temp_files/statement_2026_07.xlsx
+++ b/files/temp_files/statement_2026_07.xlsx
@@ -597,7 +597,7 @@
         <v>35</v>
       </c>
       <c r="C2">
-        <v>48.59</v>
+        <v>-48.59</v>
       </c>
       <c r="D2" t="s">
         <v>59</v>
@@ -611,7 +611,7 @@
         <v>36</v>
       </c>
       <c r="C3">
-        <v>112.11</v>
+        <v>-112.11</v>
       </c>
       <c r="D3" t="s">
         <v>60</v>
@@ -625,7 +625,7 @@
         <v>35</v>
       </c>
       <c r="C4">
-        <v>15.68</v>
+        <v>-15.68</v>
       </c>
       <c r="D4" t="s">
         <v>59</v>
@@ -639,7 +639,7 @@
         <v>37</v>
       </c>
       <c r="C5">
-        <v>7.57</v>
+        <v>-7.57</v>
       </c>
       <c r="D5" t="s">
         <v>61</v>
@@ -653,7 +653,7 @@
         <v>35</v>
       </c>
       <c r="C6">
-        <v>91.5</v>
+        <v>-91.5</v>
       </c>
       <c r="D6" t="s">
         <v>59</v>
@@ -681,7 +681,7 @@
         <v>39</v>
       </c>
       <c r="C8">
-        <v>46.16</v>
+        <v>-46.16</v>
       </c>
       <c r="D8" t="s">
         <v>63</v>
@@ -695,7 +695,7 @@
         <v>39</v>
       </c>
       <c r="C9">
-        <v>25.49</v>
+        <v>-25.49</v>
       </c>
       <c r="D9" t="s">
         <v>63</v>
@@ -709,7 +709,7 @@
         <v>40</v>
       </c>
       <c r="C10">
-        <v>118.26</v>
+        <v>-118.26</v>
       </c>
       <c r="D10" t="s">
         <v>60</v>
@@ -723,7 +723,7 @@
         <v>41</v>
       </c>
       <c r="C11">
-        <v>7.85</v>
+        <v>-7.85</v>
       </c>
       <c r="D11" t="s">
         <v>64</v>
@@ -737,7 +737,7 @@
         <v>39</v>
       </c>
       <c r="C12">
-        <v>371.45</v>
+        <v>-371.45</v>
       </c>
       <c r="D12" t="s">
         <v>63</v>
@@ -751,7 +751,7 @@
         <v>42</v>
       </c>
       <c r="C13">
-        <v>73.31999999999999</v>
+        <v>-73.31999999999999</v>
       </c>
       <c r="D13" t="s">
         <v>60</v>
@@ -765,7 +765,7 @@
         <v>43</v>
       </c>
       <c r="C14">
-        <v>167.38</v>
+        <v>-167.38</v>
       </c>
       <c r="D14" t="s">
         <v>63</v>
@@ -779,7 +779,7 @@
         <v>44</v>
       </c>
       <c r="C15">
-        <v>246.39</v>
+        <v>-246.39</v>
       </c>
       <c r="D15" t="s">
         <v>65</v>
@@ -793,7 +793,7 @@
         <v>43</v>
       </c>
       <c r="C16">
-        <v>126.77</v>
+        <v>-126.77</v>
       </c>
       <c r="D16" t="s">
         <v>63</v>
@@ -807,7 +807,7 @@
         <v>41</v>
       </c>
       <c r="C17">
-        <v>15.23</v>
+        <v>-15.23</v>
       </c>
       <c r="D17" t="s">
         <v>64</v>
@@ -821,7 +821,7 @@
         <v>45</v>
       </c>
       <c r="C18">
-        <v>187.12</v>
+        <v>-187.12</v>
       </c>
       <c r="D18" t="s">
         <v>66</v>
@@ -835,7 +835,7 @@
         <v>43</v>
       </c>
       <c r="C19">
-        <v>436.54</v>
+        <v>-436.54</v>
       </c>
       <c r="D19" t="s">
         <v>63</v>
@@ -849,7 +849,7 @@
         <v>46</v>
       </c>
       <c r="C20">
-        <v>398.56</v>
+        <v>-398.56</v>
       </c>
       <c r="D20" t="s">
         <v>61</v>
@@ -891,7 +891,7 @@
         <v>39</v>
       </c>
       <c r="C23">
-        <v>189.16</v>
+        <v>-189.16</v>
       </c>
       <c r="D23" t="s">
         <v>63</v>
@@ -919,7 +919,7 @@
         <v>48</v>
       </c>
       <c r="C25">
-        <v>170.81</v>
+        <v>-170.81</v>
       </c>
       <c r="D25" t="s">
         <v>65</v>
@@ -933,7 +933,7 @@
         <v>43</v>
       </c>
       <c r="C26">
-        <v>416.46</v>
+        <v>-416.46</v>
       </c>
       <c r="D26" t="s">
         <v>63</v>
@@ -947,7 +947,7 @@
         <v>49</v>
       </c>
       <c r="C27">
-        <v>632.9400000000001</v>
+        <v>-632.9400000000001</v>
       </c>
       <c r="D27" t="s">
         <v>61</v>
@@ -961,7 +961,7 @@
         <v>50</v>
       </c>
       <c r="C28">
-        <v>3.68</v>
+        <v>-3.68</v>
       </c>
       <c r="D28" t="s">
         <v>64</v>
@@ -975,7 +975,7 @@
         <v>37</v>
       </c>
       <c r="C29">
-        <v>592.95</v>
+        <v>-592.95</v>
       </c>
       <c r="D29" t="s">
         <v>61</v>
@@ -989,7 +989,7 @@
         <v>42</v>
       </c>
       <c r="C30">
-        <v>103.71</v>
+        <v>-103.71</v>
       </c>
       <c r="D30" t="s">
         <v>60</v>
@@ -1003,7 +1003,7 @@
         <v>51</v>
       </c>
       <c r="C31">
-        <v>82.18000000000001</v>
+        <v>-82.18000000000001</v>
       </c>
       <c r="D31" t="s">
         <v>65</v>
@@ -1017,7 +1017,7 @@
         <v>46</v>
       </c>
       <c r="C32">
-        <v>15</v>
+        <v>-15</v>
       </c>
       <c r="D32" t="s">
         <v>61</v>
@@ -1031,7 +1031,7 @@
         <v>52</v>
       </c>
       <c r="C33">
-        <v>17.32</v>
+        <v>-17.32</v>
       </c>
       <c r="D33" t="s">
         <v>59</v>
@@ -1045,7 +1045,7 @@
         <v>42</v>
       </c>
       <c r="C34">
-        <v>74.48999999999999</v>
+        <v>-74.48999999999999</v>
       </c>
       <c r="D34" t="s">
         <v>60</v>
@@ -1073,7 +1073,7 @@
         <v>48</v>
       </c>
       <c r="C36">
-        <v>267.74</v>
+        <v>-267.74</v>
       </c>
       <c r="D36" t="s">
         <v>65</v>
@@ -1087,7 +1087,7 @@
         <v>45</v>
       </c>
       <c r="C37">
-        <v>95.89</v>
+        <v>-95.89</v>
       </c>
       <c r="D37" t="s">
         <v>66</v>
@@ -1101,7 +1101,7 @@
         <v>43</v>
       </c>
       <c r="C38">
-        <v>380.54</v>
+        <v>-380.54</v>
       </c>
       <c r="D38" t="s">
         <v>63</v>
@@ -1115,7 +1115,7 @@
         <v>53</v>
       </c>
       <c r="C39">
-        <v>25.39</v>
+        <v>-25.39</v>
       </c>
       <c r="D39" t="s">
         <v>59</v>
@@ -1129,7 +1129,7 @@
         <v>49</v>
       </c>
       <c r="C40">
-        <v>229.79</v>
+        <v>-229.79</v>
       </c>
       <c r="D40" t="s">
         <v>61</v>
@@ -1143,7 +1143,7 @@
         <v>46</v>
       </c>
       <c r="C41">
-        <v>755.37</v>
+        <v>-755.37</v>
       </c>
       <c r="D41" t="s">
         <v>61</v>
@@ -1157,7 +1157,7 @@
         <v>37</v>
       </c>
       <c r="C42">
-        <v>373.31</v>
+        <v>-373.31</v>
       </c>
       <c r="D42" t="s">
         <v>61</v>
@@ -1171,7 +1171,7 @@
         <v>54</v>
       </c>
       <c r="C43">
-        <v>149.22</v>
+        <v>-149.22</v>
       </c>
       <c r="D43" t="s">
         <v>66</v>
@@ -1199,7 +1199,7 @@
         <v>46</v>
       </c>
       <c r="C45">
-        <v>524.64</v>
+        <v>-524.64</v>
       </c>
       <c r="D45" t="s">
         <v>61</v>
@@ -1241,7 +1241,7 @@
         <v>44</v>
       </c>
       <c r="C48">
-        <v>193.72</v>
+        <v>-193.72</v>
       </c>
       <c r="D48" t="s">
         <v>65</v>
@@ -1255,7 +1255,7 @@
         <v>55</v>
       </c>
       <c r="C49">
-        <v>458.71</v>
+        <v>-458.71</v>
       </c>
       <c r="D49" t="s">
         <v>63</v>
@@ -1297,7 +1297,7 @@
         <v>53</v>
       </c>
       <c r="C52">
-        <v>79.81999999999999</v>
+        <v>-79.81999999999999</v>
       </c>
       <c r="D52" t="s">
         <v>59</v>
@@ -1311,7 +1311,7 @@
         <v>36</v>
       </c>
       <c r="C53">
-        <v>59.49</v>
+        <v>-59.49</v>
       </c>
       <c r="D53" t="s">
         <v>60</v>
@@ -1325,7 +1325,7 @@
         <v>54</v>
       </c>
       <c r="C54">
-        <v>88.66</v>
+        <v>-88.66</v>
       </c>
       <c r="D54" t="s">
         <v>66</v>
@@ -1339,7 +1339,7 @@
         <v>41</v>
       </c>
       <c r="C55">
-        <v>35.1</v>
+        <v>-35.1</v>
       </c>
       <c r="D55" t="s">
         <v>64</v>
@@ -1353,7 +1353,7 @@
         <v>43</v>
       </c>
       <c r="C56">
-        <v>222.16</v>
+        <v>-222.16</v>
       </c>
       <c r="D56" t="s">
         <v>63</v>
@@ -1381,7 +1381,7 @@
         <v>46</v>
       </c>
       <c r="C58">
-        <v>520.15</v>
+        <v>-520.15</v>
       </c>
       <c r="D58" t="s">
         <v>61</v>
@@ -1395,7 +1395,7 @@
         <v>36</v>
       </c>
       <c r="C59">
-        <v>82.75</v>
+        <v>-82.75</v>
       </c>
       <c r="D59" t="s">
         <v>60</v>
@@ -1409,7 +1409,7 @@
         <v>36</v>
       </c>
       <c r="C60">
-        <v>26.58</v>
+        <v>-26.58</v>
       </c>
       <c r="D60" t="s">
         <v>60</v>
@@ -1437,7 +1437,7 @@
         <v>48</v>
       </c>
       <c r="C62">
-        <v>165.25</v>
+        <v>-165.25</v>
       </c>
       <c r="D62" t="s">
         <v>65</v>
@@ -1451,7 +1451,7 @@
         <v>40</v>
       </c>
       <c r="C63">
-        <v>126.34</v>
+        <v>-126.34</v>
       </c>
       <c r="D63" t="s">
         <v>60</v>
@@ -1465,7 +1465,7 @@
         <v>35</v>
       </c>
       <c r="C64">
-        <v>37.42</v>
+        <v>-37.42</v>
       </c>
       <c r="D64" t="s">
         <v>59</v>
@@ -1479,7 +1479,7 @@
         <v>54</v>
       </c>
       <c r="C65">
-        <v>135.69</v>
+        <v>-135.69</v>
       </c>
       <c r="D65" t="s">
         <v>66</v>
@@ -1493,7 +1493,7 @@
         <v>57</v>
       </c>
       <c r="C66">
-        <v>33.75</v>
+        <v>-33.75</v>
       </c>
       <c r="D66" t="s">
         <v>64</v>
@@ -1507,7 +1507,7 @@
         <v>42</v>
       </c>
       <c r="C67">
-        <v>77.98999999999999</v>
+        <v>-77.98999999999999</v>
       </c>
       <c r="D67" t="s">
         <v>60</v>
@@ -1521,7 +1521,7 @@
         <v>46</v>
       </c>
       <c r="C68">
-        <v>126.82</v>
+        <v>-126.82</v>
       </c>
       <c r="D68" t="s">
         <v>61</v>
@@ -1535,7 +1535,7 @@
         <v>44</v>
       </c>
       <c r="C69">
-        <v>68.54000000000001</v>
+        <v>-68.54000000000001</v>
       </c>
       <c r="D69" t="s">
         <v>65</v>
@@ -1549,7 +1549,7 @@
         <v>50</v>
       </c>
       <c r="C70">
-        <v>25.21</v>
+        <v>-25.21</v>
       </c>
       <c r="D70" t="s">
         <v>64</v>
@@ -1563,7 +1563,7 @@
         <v>57</v>
       </c>
       <c r="C71">
-        <v>24.84</v>
+        <v>-24.84</v>
       </c>
       <c r="D71" t="s">
         <v>64</v>
@@ -1577,7 +1577,7 @@
         <v>46</v>
       </c>
       <c r="C72">
-        <v>992.29</v>
+        <v>-992.29</v>
       </c>
       <c r="D72" t="s">
         <v>61</v>
@@ -1591,7 +1591,7 @@
         <v>55</v>
       </c>
       <c r="C73">
-        <v>211.78</v>
+        <v>-211.78</v>
       </c>
       <c r="D73" t="s">
         <v>63</v>
@@ -1619,7 +1619,7 @@
         <v>50</v>
       </c>
       <c r="C75">
-        <v>40.28</v>
+        <v>-40.28</v>
       </c>
       <c r="D75" t="s">
         <v>64</v>
@@ -1661,7 +1661,7 @@
         <v>57</v>
       </c>
       <c r="C78">
-        <v>8.960000000000001</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="D78" t="s">
         <v>64</v>
@@ -1675,7 +1675,7 @@
         <v>52</v>
       </c>
       <c r="C79">
-        <v>62.32</v>
+        <v>-62.32</v>
       </c>
       <c r="D79" t="s">
         <v>59</v>
@@ -1689,7 +1689,7 @@
         <v>42</v>
       </c>
       <c r="C80">
-        <v>29.63</v>
+        <v>-29.63</v>
       </c>
       <c r="D80" t="s">
         <v>60</v>
@@ -1703,7 +1703,7 @@
         <v>54</v>
       </c>
       <c r="C81">
-        <v>173.2</v>
+        <v>-173.2</v>
       </c>
       <c r="D81" t="s">
         <v>66</v>
@@ -1717,7 +1717,7 @@
         <v>50</v>
       </c>
       <c r="C82">
-        <v>2.03</v>
+        <v>-2.03</v>
       </c>
       <c r="D82" t="s">
         <v>64</v>
@@ -1731,7 +1731,7 @@
         <v>55</v>
       </c>
       <c r="C83">
-        <v>238.39</v>
+        <v>-238.39</v>
       </c>
       <c r="D83" t="s">
         <v>63</v>
@@ -1745,7 +1745,7 @@
         <v>44</v>
       </c>
       <c r="C84">
-        <v>262.78</v>
+        <v>-262.78</v>
       </c>
       <c r="D84" t="s">
         <v>65</v>
@@ -1759,7 +1759,7 @@
         <v>51</v>
       </c>
       <c r="C85">
-        <v>283.89</v>
+        <v>-283.89</v>
       </c>
       <c r="D85" t="s">
         <v>65</v>
@@ -1773,7 +1773,7 @@
         <v>39</v>
       </c>
       <c r="C86">
-        <v>314.46</v>
+        <v>-314.46</v>
       </c>
       <c r="D86" t="s">
         <v>63</v>
@@ -1787,7 +1787,7 @@
         <v>41</v>
       </c>
       <c r="C87">
-        <v>23.28</v>
+        <v>-23.28</v>
       </c>
       <c r="D87" t="s">
         <v>64</v>
@@ -1801,7 +1801,7 @@
         <v>54</v>
       </c>
       <c r="C88">
-        <v>74</v>
+        <v>-74</v>
       </c>
       <c r="D88" t="s">
         <v>66</v>
@@ -1815,7 +1815,7 @@
         <v>48</v>
       </c>
       <c r="C89">
-        <v>179.35</v>
+        <v>-179.35</v>
       </c>
       <c r="D89" t="s">
         <v>65</v>
@@ -1829,7 +1829,7 @@
         <v>57</v>
       </c>
       <c r="C90">
-        <v>47.86</v>
+        <v>-47.86</v>
       </c>
       <c r="D90" t="s">
         <v>64</v>
@@ -1843,7 +1843,7 @@
         <v>39</v>
       </c>
       <c r="C91">
-        <v>85.11</v>
+        <v>-85.11</v>
       </c>
       <c r="D91" t="s">
         <v>63</v>
@@ -1857,7 +1857,7 @@
         <v>37</v>
       </c>
       <c r="C92">
-        <v>240.94</v>
+        <v>-240.94</v>
       </c>
       <c r="D92" t="s">
         <v>61</v>
@@ -1871,7 +1871,7 @@
         <v>48</v>
       </c>
       <c r="C93">
-        <v>268.95</v>
+        <v>-268.95</v>
       </c>
       <c r="D93" t="s">
         <v>65</v>
@@ -1885,7 +1885,7 @@
         <v>42</v>
       </c>
       <c r="C94">
-        <v>70.63</v>
+        <v>-70.63</v>
       </c>
       <c r="D94" t="s">
         <v>60</v>
@@ -1899,7 +1899,7 @@
         <v>54</v>
       </c>
       <c r="C95">
-        <v>185.27</v>
+        <v>-185.27</v>
       </c>
       <c r="D95" t="s">
         <v>66</v>
@@ -1913,7 +1913,7 @@
         <v>49</v>
       </c>
       <c r="C96">
-        <v>649.26</v>
+        <v>-649.26</v>
       </c>
       <c r="D96" t="s">
         <v>61</v>
@@ -1927,7 +1927,7 @@
         <v>42</v>
       </c>
       <c r="C97">
-        <v>136.37</v>
+        <v>-136.37</v>
       </c>
       <c r="D97" t="s">
         <v>60</v>
@@ -1941,7 +1941,7 @@
         <v>40</v>
       </c>
       <c r="C98">
-        <v>48.8</v>
+        <v>-48.8</v>
       </c>
       <c r="D98" t="s">
         <v>60</v>
@@ -1955,7 +1955,7 @@
         <v>42</v>
       </c>
       <c r="C99">
-        <v>102.34</v>
+        <v>-102.34</v>
       </c>
       <c r="D99" t="s">
         <v>60</v>
@@ -1969,7 +1969,7 @@
         <v>42</v>
       </c>
       <c r="C100">
-        <v>74.13</v>
+        <v>-74.13</v>
       </c>
       <c r="D100" t="s">
         <v>60</v>
@@ -1997,7 +1997,7 @@
         <v>49</v>
       </c>
       <c r="C102">
-        <v>497.74</v>
+        <v>-497.74</v>
       </c>
       <c r="D102" t="s">
         <v>61</v>
@@ -2011,7 +2011,7 @@
         <v>53</v>
       </c>
       <c r="C103">
-        <v>17.43</v>
+        <v>-17.43</v>
       </c>
       <c r="D103" t="s">
         <v>59</v>
@@ -2025,7 +2025,7 @@
         <v>46</v>
       </c>
       <c r="C104">
-        <v>442.96</v>
+        <v>-442.96</v>
       </c>
       <c r="D104" t="s">
         <v>61</v>
@@ -2039,7 +2039,7 @@
         <v>43</v>
       </c>
       <c r="C105">
-        <v>207.75</v>
+        <v>-207.75</v>
       </c>
       <c r="D105" t="s">
         <v>63</v>
@@ -2053,7 +2053,7 @@
         <v>43</v>
       </c>
       <c r="C106">
-        <v>173.96</v>
+        <v>-173.96</v>
       </c>
       <c r="D106" t="s">
         <v>63</v>
@@ -2081,7 +2081,7 @@
         <v>50</v>
       </c>
       <c r="C108">
-        <v>10.81</v>
+        <v>-10.81</v>
       </c>
       <c r="D108" t="s">
         <v>64</v>
@@ -2095,7 +2095,7 @@
         <v>58</v>
       </c>
       <c r="C109">
-        <v>53.83</v>
+        <v>-53.83</v>
       </c>
       <c r="D109" t="s">
         <v>66</v>
@@ -2109,7 +2109,7 @@
         <v>49</v>
       </c>
       <c r="C110">
-        <v>637.14</v>
+        <v>-637.14</v>
       </c>
       <c r="D110" t="s">
         <v>61</v>
@@ -2123,7 +2123,7 @@
         <v>55</v>
       </c>
       <c r="C111">
-        <v>357.05</v>
+        <v>-357.05</v>
       </c>
       <c r="D111" t="s">
         <v>63</v>
@@ -2137,7 +2137,7 @@
         <v>42</v>
       </c>
       <c r="C112">
-        <v>37.24</v>
+        <v>-37.24</v>
       </c>
       <c r="D112" t="s">
         <v>60</v>
@@ -2165,7 +2165,7 @@
         <v>35</v>
       </c>
       <c r="C114">
-        <v>16.99</v>
+        <v>-16.99</v>
       </c>
       <c r="D114" t="s">
         <v>59</v>
@@ -2179,7 +2179,7 @@
         <v>36</v>
       </c>
       <c r="C115">
-        <v>56.64</v>
+        <v>-56.64</v>
       </c>
       <c r="D115" t="s">
         <v>60</v>
@@ -2193,7 +2193,7 @@
         <v>51</v>
       </c>
       <c r="C116">
-        <v>140.6</v>
+        <v>-140.6</v>
       </c>
       <c r="D116" t="s">
         <v>65</v>
@@ -2207,7 +2207,7 @@
         <v>49</v>
       </c>
       <c r="C117">
-        <v>24.97</v>
+        <v>-24.97</v>
       </c>
       <c r="D117" t="s">
         <v>61</v>
@@ -2221,7 +2221,7 @@
         <v>39</v>
       </c>
       <c r="C118">
-        <v>249.9</v>
+        <v>-249.9</v>
       </c>
       <c r="D118" t="s">
         <v>63</v>
@@ -2235,7 +2235,7 @@
         <v>49</v>
       </c>
       <c r="C119">
-        <v>309.2</v>
+        <v>-309.2</v>
       </c>
       <c r="D119" t="s">
         <v>61</v>
@@ -2249,7 +2249,7 @@
         <v>50</v>
       </c>
       <c r="C120">
-        <v>19.62</v>
+        <v>-19.62</v>
       </c>
       <c r="D120" t="s">
         <v>64</v>
@@ -2263,7 +2263,7 @@
         <v>39</v>
       </c>
       <c r="C121">
-        <v>93.47</v>
+        <v>-93.47</v>
       </c>
       <c r="D121" t="s">
         <v>63</v>
@@ -2277,7 +2277,7 @@
         <v>42</v>
       </c>
       <c r="C122">
-        <v>25.95</v>
+        <v>-25.95</v>
       </c>
       <c r="D122" t="s">
         <v>60</v>
@@ -2291,7 +2291,7 @@
         <v>49</v>
       </c>
       <c r="C123">
-        <v>909.21</v>
+        <v>-909.21</v>
       </c>
       <c r="D123" t="s">
         <v>61</v>
@@ -2333,7 +2333,7 @@
         <v>42</v>
       </c>
       <c r="C126">
-        <v>68.51000000000001</v>
+        <v>-68.51000000000001</v>
       </c>
       <c r="D126" t="s">
         <v>60</v>
@@ -2347,7 +2347,7 @@
         <v>51</v>
       </c>
       <c r="C127">
-        <v>141.76</v>
+        <v>-141.76</v>
       </c>
       <c r="D127" t="s">
         <v>65</v>
@@ -2361,7 +2361,7 @@
         <v>52</v>
       </c>
       <c r="C128">
-        <v>84.05</v>
+        <v>-84.05</v>
       </c>
       <c r="D128" t="s">
         <v>59</v>
@@ -2375,7 +2375,7 @@
         <v>54</v>
       </c>
       <c r="C129">
-        <v>129.72</v>
+        <v>-129.72</v>
       </c>
       <c r="D129" t="s">
         <v>66</v>
@@ -2403,7 +2403,7 @@
         <v>51</v>
       </c>
       <c r="C131">
-        <v>286.03</v>
+        <v>-286.03</v>
       </c>
       <c r="D131" t="s">
         <v>65</v>
@@ -2417,7 +2417,7 @@
         <v>54</v>
       </c>
       <c r="C132">
-        <v>135.85</v>
+        <v>-135.85</v>
       </c>
       <c r="D132" t="s">
         <v>66</v>
@@ -2431,7 +2431,7 @@
         <v>51</v>
       </c>
       <c r="C133">
-        <v>55.48</v>
+        <v>-55.48</v>
       </c>
       <c r="D133" t="s">
         <v>65</v>
@@ -2445,7 +2445,7 @@
         <v>42</v>
       </c>
       <c r="C134">
-        <v>76.04000000000001</v>
+        <v>-76.04000000000001</v>
       </c>
       <c r="D134" t="s">
         <v>60</v>
@@ -2459,7 +2459,7 @@
         <v>41</v>
       </c>
       <c r="C135">
-        <v>5.63</v>
+        <v>-5.63</v>
       </c>
       <c r="D135" t="s">
         <v>64</v>
@@ -2487,7 +2487,7 @@
         <v>37</v>
       </c>
       <c r="C137">
-        <v>901.26</v>
+        <v>-901.26</v>
       </c>
       <c r="D137" t="s">
         <v>61</v>
@@ -2501,7 +2501,7 @@
         <v>43</v>
       </c>
       <c r="C138">
-        <v>223.2</v>
+        <v>-223.2</v>
       </c>
       <c r="D138" t="s">
         <v>63</v>
@@ -2515,7 +2515,7 @@
         <v>41</v>
       </c>
       <c r="C139">
-        <v>43.37</v>
+        <v>-43.37</v>
       </c>
       <c r="D139" t="s">
         <v>64</v>
@@ -2529,7 +2529,7 @@
         <v>54</v>
       </c>
       <c r="C140">
-        <v>124.71</v>
+        <v>-124.71</v>
       </c>
       <c r="D140" t="s">
         <v>66</v>
@@ -2543,7 +2543,7 @@
         <v>55</v>
       </c>
       <c r="C141">
-        <v>10.47</v>
+        <v>-10.47</v>
       </c>
       <c r="D141" t="s">
         <v>63</v>
@@ -2557,7 +2557,7 @@
         <v>40</v>
       </c>
       <c r="C142">
-        <v>85.94</v>
+        <v>-85.94</v>
       </c>
       <c r="D142" t="s">
         <v>60</v>
@@ -2571,7 +2571,7 @@
         <v>39</v>
       </c>
       <c r="C143">
-        <v>185.31</v>
+        <v>-185.31</v>
       </c>
       <c r="D143" t="s">
         <v>63</v>
@@ -2585,7 +2585,7 @@
         <v>52</v>
       </c>
       <c r="C144">
-        <v>80.38</v>
+        <v>-80.38</v>
       </c>
       <c r="D144" t="s">
         <v>59</v>
@@ -2599,7 +2599,7 @@
         <v>46</v>
       </c>
       <c r="C145">
-        <v>842.28</v>
+        <v>-842.28</v>
       </c>
       <c r="D145" t="s">
         <v>61</v>
@@ -2613,7 +2613,7 @@
         <v>50</v>
       </c>
       <c r="C146">
-        <v>12.14</v>
+        <v>-12.14</v>
       </c>
       <c r="D146" t="s">
         <v>64</v>
@@ -2655,7 +2655,7 @@
         <v>40</v>
       </c>
       <c r="C149">
-        <v>100.82</v>
+        <v>-100.82</v>
       </c>
       <c r="D149" t="s">
         <v>60</v>
@@ -2669,7 +2669,7 @@
         <v>52</v>
       </c>
       <c r="C150">
-        <v>18.8</v>
+        <v>-18.8</v>
       </c>
       <c r="D150" t="s">
         <v>59</v>
@@ -2697,7 +2697,7 @@
         <v>40</v>
       </c>
       <c r="C152">
-        <v>31.51</v>
+        <v>-31.51</v>
       </c>
       <c r="D152" t="s">
         <v>60</v>
@@ -2725,7 +2725,7 @@
         <v>37</v>
       </c>
       <c r="C154">
-        <v>903.78</v>
+        <v>-903.78</v>
       </c>
       <c r="D154" t="s">
         <v>61</v>
@@ -2739,7 +2739,7 @@
         <v>57</v>
       </c>
       <c r="C155">
-        <v>14.09</v>
+        <v>-14.09</v>
       </c>
       <c r="D155" t="s">
         <v>64</v>
@@ -2753,7 +2753,7 @@
         <v>36</v>
       </c>
       <c r="C156">
-        <v>108.54</v>
+        <v>-108.54</v>
       </c>
       <c r="D156" t="s">
         <v>60</v>
@@ -2767,7 +2767,7 @@
         <v>53</v>
       </c>
       <c r="C157">
-        <v>69.13</v>
+        <v>-69.13</v>
       </c>
       <c r="D157" t="s">
         <v>59</v>
@@ -2781,7 +2781,7 @@
         <v>58</v>
       </c>
       <c r="C158">
-        <v>19.19</v>
+        <v>-19.19</v>
       </c>
       <c r="D158" t="s">
         <v>66</v>
@@ -2795,7 +2795,7 @@
         <v>44</v>
       </c>
       <c r="C159">
-        <v>282.39</v>
+        <v>-282.39</v>
       </c>
       <c r="D159" t="s">
         <v>65</v>
@@ -2809,7 +2809,7 @@
         <v>52</v>
       </c>
       <c r="C160">
-        <v>60.12</v>
+        <v>-60.12</v>
       </c>
       <c r="D160" t="s">
         <v>59</v>
@@ -2823,7 +2823,7 @@
         <v>57</v>
       </c>
       <c r="C161">
-        <v>32.82</v>
+        <v>-32.82</v>
       </c>
       <c r="D161" t="s">
         <v>64</v>
@@ -2837,7 +2837,7 @@
         <v>41</v>
       </c>
       <c r="C162">
-        <v>2.52</v>
+        <v>-2.52</v>
       </c>
       <c r="D162" t="s">
         <v>64</v>
@@ -2851,7 +2851,7 @@
         <v>44</v>
       </c>
       <c r="C163">
-        <v>145.85</v>
+        <v>-145.85</v>
       </c>
       <c r="D163" t="s">
         <v>65</v>
@@ -2865,7 +2865,7 @@
         <v>46</v>
       </c>
       <c r="C164">
-        <v>277.38</v>
+        <v>-277.38</v>
       </c>
       <c r="D164" t="s">
         <v>61</v>
@@ -2879,7 +2879,7 @@
         <v>35</v>
       </c>
       <c r="C165">
-        <v>93.97</v>
+        <v>-93.97</v>
       </c>
       <c r="D165" t="s">
         <v>59</v>
@@ -2893,7 +2893,7 @@
         <v>48</v>
       </c>
       <c r="C166">
-        <v>295.29</v>
+        <v>-295.29</v>
       </c>
       <c r="D166" t="s">
         <v>65</v>
@@ -2907,7 +2907,7 @@
         <v>41</v>
       </c>
       <c r="C167">
-        <v>34.72</v>
+        <v>-34.72</v>
       </c>
       <c r="D167" t="s">
         <v>64</v>
@@ -2921,7 +2921,7 @@
         <v>37</v>
       </c>
       <c r="C168">
-        <v>782.42</v>
+        <v>-782.42</v>
       </c>
       <c r="D168" t="s">
         <v>61</v>
@@ -2935,7 +2935,7 @@
         <v>44</v>
       </c>
       <c r="C169">
-        <v>171.18</v>
+        <v>-171.18</v>
       </c>
       <c r="D169" t="s">
         <v>65</v>
@@ -2949,7 +2949,7 @@
         <v>40</v>
       </c>
       <c r="C170">
-        <v>107.59</v>
+        <v>-107.59</v>
       </c>
       <c r="D170" t="s">
         <v>60</v>
@@ -2963,7 +2963,7 @@
         <v>57</v>
       </c>
       <c r="C171">
-        <v>27.89</v>
+        <v>-27.89</v>
       </c>
       <c r="D171" t="s">
         <v>64</v>
@@ -2977,7 +2977,7 @@
         <v>44</v>
       </c>
       <c r="C172">
-        <v>152.25</v>
+        <v>-152.25</v>
       </c>
       <c r="D172" t="s">
         <v>65</v>
@@ -2991,7 +2991,7 @@
         <v>52</v>
       </c>
       <c r="C173">
-        <v>80.86</v>
+        <v>-80.86</v>
       </c>
       <c r="D173" t="s">
         <v>59</v>
@@ -3005,7 +3005,7 @@
         <v>41</v>
       </c>
       <c r="C174">
-        <v>30.57</v>
+        <v>-30.57</v>
       </c>
       <c r="D174" t="s">
         <v>64</v>
@@ -3033,7 +3033,7 @@
         <v>42</v>
       </c>
       <c r="C176">
-        <v>124.36</v>
+        <v>-124.36</v>
       </c>
       <c r="D176" t="s">
         <v>60</v>
@@ -3047,7 +3047,7 @@
         <v>43</v>
       </c>
       <c r="C177">
-        <v>341.79</v>
+        <v>-341.79</v>
       </c>
       <c r="D177" t="s">
         <v>63</v>
@@ -3061,7 +3061,7 @@
         <v>48</v>
       </c>
       <c r="C178">
-        <v>144.36</v>
+        <v>-144.36</v>
       </c>
       <c r="D178" t="s">
         <v>65</v>
@@ -3075,7 +3075,7 @@
         <v>43</v>
       </c>
       <c r="C179">
-        <v>142.68</v>
+        <v>-142.68</v>
       </c>
       <c r="D179" t="s">
         <v>63</v>
@@ -3103,7 +3103,7 @@
         <v>52</v>
       </c>
       <c r="C181">
-        <v>87.78</v>
+        <v>-87.78</v>
       </c>
       <c r="D181" t="s">
         <v>59</v>
@@ -3117,7 +3117,7 @@
         <v>37</v>
       </c>
       <c r="C182">
-        <v>469.73</v>
+        <v>-469.73</v>
       </c>
       <c r="D182" t="s">
         <v>61</v>
@@ -3131,7 +3131,7 @@
         <v>48</v>
       </c>
       <c r="C183">
-        <v>39.4</v>
+        <v>-39.4</v>
       </c>
       <c r="D183" t="s">
         <v>65</v>
@@ -3145,7 +3145,7 @@
         <v>49</v>
       </c>
       <c r="C184">
-        <v>137.88</v>
+        <v>-137.88</v>
       </c>
       <c r="D184" t="s">
         <v>61</v>
@@ -3159,7 +3159,7 @@
         <v>51</v>
       </c>
       <c r="C185">
-        <v>43.93</v>
+        <v>-43.93</v>
       </c>
       <c r="D185" t="s">
         <v>65</v>
@@ -3187,7 +3187,7 @@
         <v>50</v>
       </c>
       <c r="C187">
-        <v>35.56</v>
+        <v>-35.56</v>
       </c>
       <c r="D187" t="s">
         <v>64</v>
@@ -3215,7 +3215,7 @@
         <v>41</v>
       </c>
       <c r="C189">
-        <v>27.38</v>
+        <v>-27.38</v>
       </c>
       <c r="D189" t="s">
         <v>64</v>
@@ -3229,7 +3229,7 @@
         <v>41</v>
       </c>
       <c r="C190">
-        <v>20.4</v>
+        <v>-20.4</v>
       </c>
       <c r="D190" t="s">
         <v>64</v>
@@ -3257,7 +3257,7 @@
         <v>44</v>
       </c>
       <c r="C192">
-        <v>254.17</v>
+        <v>-254.17</v>
       </c>
       <c r="D192" t="s">
         <v>65</v>
@@ -3271,7 +3271,7 @@
         <v>35</v>
       </c>
       <c r="C193">
-        <v>28.26</v>
+        <v>-28.26</v>
       </c>
       <c r="D193" t="s">
         <v>59</v>
@@ -3285,7 +3285,7 @@
         <v>57</v>
       </c>
       <c r="C194">
-        <v>9.26</v>
+        <v>-9.26</v>
       </c>
       <c r="D194" t="s">
         <v>64</v>
@@ -3299,7 +3299,7 @@
         <v>35</v>
       </c>
       <c r="C195">
-        <v>42.19</v>
+        <v>-42.19</v>
       </c>
       <c r="D195" t="s">
         <v>59</v>
@@ -3313,7 +3313,7 @@
         <v>40</v>
       </c>
       <c r="C196">
-        <v>25.82</v>
+        <v>-25.82</v>
       </c>
       <c r="D196" t="s">
         <v>60</v>
@@ -3327,7 +3327,7 @@
         <v>54</v>
       </c>
       <c r="C197">
-        <v>94.25</v>
+        <v>-94.25</v>
       </c>
       <c r="D197" t="s">
         <v>66</v>
@@ -3341,7 +3341,7 @@
         <v>42</v>
       </c>
       <c r="C198">
-        <v>40.76</v>
+        <v>-40.76</v>
       </c>
       <c r="D198" t="s">
         <v>60</v>
@@ -3355,7 +3355,7 @@
         <v>45</v>
       </c>
       <c r="C199">
-        <v>185.82</v>
+        <v>-185.82</v>
       </c>
       <c r="D199" t="s">
         <v>66</v>
@@ -3369,7 +3369,7 @@
         <v>58</v>
       </c>
       <c r="C200">
-        <v>14.86</v>
+        <v>-14.86</v>
       </c>
       <c r="D200" t="s">
         <v>66</v>
@@ -3383,7 +3383,7 @@
         <v>44</v>
       </c>
       <c r="C201">
-        <v>281.9</v>
+        <v>-281.9</v>
       </c>
       <c r="D201" t="s">
         <v>65</v>
